--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39C.xlsx
@@ -1,20 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_A8276F5FD2D75CB38564C7DB4B66239DDA8481A5" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{A1ED568F-9372-459D-9E36-F68B5FBD1583}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
+    <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="Hidden_17">Hidden_1!$A$1:$A$2</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="84">
   <si>
     <t>49008</t>
   </si>
@@ -40,6 +50,9 @@
     <t>4</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -67,6 +80,9 @@
     <t>436963</t>
   </si>
   <si>
+    <t>571944</t>
+  </si>
+  <si>
     <t>436951</t>
   </si>
   <si>
@@ -109,6 +125,9 @@
     <t>Segundo apellido</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/01/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Cargo o puesto que ocupa en el sujeto obligado</t>
   </si>
   <si>
@@ -130,19 +149,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>630A6F92739382F8246AD8BFC8A6E455</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
-    <t>Antonio Eduardo</t>
+    <t>2023</t>
   </si>
   <si>
     <t>González</t>
@@ -151,133 +158,130 @@
     <t>Betancour</t>
   </si>
   <si>
-    <t>Jefe de oficina</t>
-  </si>
-  <si>
-    <t>Vocal I</t>
+    <t/>
   </si>
   <si>
     <t>transparencia@cobatlaxcala.edu.mx</t>
   </si>
   <si>
+    <t>Bautista</t>
+  </si>
+  <si>
+    <t>Hernández</t>
+  </si>
+  <si>
+    <t>sistemas@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>Pérez</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Lic. Eduardo Antonio</t>
+  </si>
+  <si>
+    <t>Lic. Jose Humberto</t>
+  </si>
+  <si>
+    <t>Cuellar</t>
+  </si>
+  <si>
+    <t>Jefe del Departamento de Recursos Materiales</t>
+  </si>
+  <si>
+    <t>Vocal I del Comité</t>
+  </si>
+  <si>
+    <t>Rec.Materiales@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
     <t>Área de Transparencia</t>
   </si>
   <si>
-    <t>11/01/2023</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>075281599C743AEDE04B6AD6198B46A0</t>
-  </si>
-  <si>
-    <t>Josè Alberto</t>
-  </si>
-  <si>
-    <t>Hernandez</t>
-  </si>
-  <si>
-    <t>Bautista</t>
-  </si>
-  <si>
-    <t>Resposnable de Sistemas</t>
-  </si>
-  <si>
-    <t>Vocal IV</t>
-  </si>
-  <si>
-    <t>sistemas@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>7F1DD09BA6F0D588D9285332AD2BDF1E</t>
-  </si>
-  <si>
-    <t>Maximo Oscar</t>
-  </si>
-  <si>
-    <t>Luna</t>
-  </si>
-  <si>
-    <t>Capilla</t>
-  </si>
-  <si>
-    <t>Contralor Interno</t>
-  </si>
-  <si>
-    <t>Vocal III</t>
-  </si>
-  <si>
-    <t>contraloria@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>DA631FEA0ED290518D1685F3EC962420</t>
-  </si>
-  <si>
-    <t>Oscar</t>
-  </si>
-  <si>
-    <t>Lobatón</t>
-  </si>
-  <si>
-    <t>Corona</t>
-  </si>
-  <si>
-    <t>Subdirector Juridico</t>
-  </si>
-  <si>
-    <t>Vocal II</t>
-  </si>
-  <si>
-    <t>juridico@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>A4FDF4EC5C53E80B4A57597F7F14D88C</t>
-  </si>
-  <si>
-    <t>Carlos Francisco</t>
-  </si>
-  <si>
-    <t>Fernandez</t>
-  </si>
-  <si>
-    <t>Salas</t>
-  </si>
-  <si>
-    <t>Director Administrativo</t>
-  </si>
-  <si>
-    <t>Secretario</t>
-  </si>
-  <si>
-    <t>diradmon@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>C5AC27FBB1B9B155A8F443F9A2A456D1</t>
-  </si>
-  <si>
-    <t>Darwin</t>
-  </si>
-  <si>
-    <t>Perez</t>
-  </si>
-  <si>
-    <t>Y Perez</t>
-  </si>
-  <si>
-    <t>Director General</t>
-  </si>
-  <si>
-    <t>Presidente</t>
-  </si>
-  <si>
-    <t>dir.general@cobatlaxcala.edu.mx</t>
+    <t>Ing. Jose Alberto</t>
+  </si>
+  <si>
+    <t>Responsable de Sistemas y Organización</t>
+  </si>
+  <si>
+    <t>Vocal II del Comité</t>
+  </si>
+  <si>
+    <t>Lic. Antonio Heber</t>
+  </si>
+  <si>
+    <t>García</t>
+  </si>
+  <si>
+    <t>Mendez</t>
+  </si>
+  <si>
+    <t>Integrante de la Dirección Academica</t>
+  </si>
+  <si>
+    <t>Vocal III del Comité</t>
+  </si>
+  <si>
+    <t>Dir.Academica@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>Secretario del Comité</t>
+  </si>
+  <si>
+    <t>106414D4C550911F349573B9EEA4FB55</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>Mtra. Cecelia Mariel</t>
+  </si>
+  <si>
+    <t>Trinidad</t>
+  </si>
+  <si>
+    <t>Corro</t>
+  </si>
+  <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t>Jefa del Departamento de Recursos Humanos</t>
+  </si>
+  <si>
+    <t>Presidenta del Comité</t>
+  </si>
+  <si>
+    <t>Rec.Humanos@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>10/01/2024</t>
+  </si>
+  <si>
+    <t>88F1401A0554A58A18F62747993C2645</t>
+  </si>
+  <si>
+    <t>Responsable del Área de Transparencia</t>
+  </si>
+  <si>
+    <t>BE9497829A65C274CECBB531FBF5565D</t>
+  </si>
+  <si>
+    <t>74C8D09988003C178F7EB365E14C3E90</t>
+  </si>
+  <si>
+    <t>3C002589D7FFB67659BAFCB5E6E3789D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -373,6 +377,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -388,44 +395,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -453,14 +460,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -488,6 +512,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -499,196 +540,173 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="55.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="55.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -705,7 +723,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -720,7 +738,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -740,7 +758,7 @@
         <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I4" t="s">
         <v>6</v>
@@ -749,62 +767,68 @@
         <v>6</v>
       </c>
       <c r="K4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" t="s">
         <v>7</v>
-      </c>
-      <c r="M4" t="s">
-        <v>9</v>
       </c>
       <c r="N4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="O5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -819,315 +843,290 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-    </row>
-    <row r="7" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="2" t="s">
+    </row>
+    <row r="10" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N8" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>48</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="N11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="J12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="N12" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>50</v>
+        <v>78</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:N6"/>
+    <mergeCell ref="A6:O6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1135,6 +1134,31 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H186" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>Hidden_17</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>